--- a/salidas/empresas/MRNA.xlsx
+++ b/salidas/empresas/MRNA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,54 +447,54 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B2" t="n">
@@ -501,7 +513,7 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B3" t="n">
@@ -520,7 +532,7 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B4" t="n">
@@ -539,7 +551,7 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B5" t="n">
@@ -566,7 +578,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B6" t="n">
@@ -593,7 +605,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B7" t="n">
@@ -620,7 +632,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B8" t="n">
@@ -647,7 +659,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B9" t="n">
@@ -674,7 +686,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B10" t="n">
@@ -701,7 +713,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B11" t="n">
@@ -728,7 +740,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B12" t="n">
@@ -755,7 +767,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B13" t="n">
@@ -782,7 +794,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B14" t="n">
@@ -809,7 +821,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B15" t="n">
@@ -836,7 +848,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B16" t="n">
@@ -863,7 +875,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B17" t="n">
@@ -890,7 +902,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B18" t="n">
@@ -917,7 +929,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B19" t="n">
@@ -944,7 +956,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B20" t="n">
@@ -971,7 +983,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B21" t="n">
@@ -998,7 +1010,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B22" t="n">
@@ -1025,7 +1037,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B23" t="n">
@@ -1052,7 +1064,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B24" t="n">
@@ -1077,7 +1089,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B25" t="n">
@@ -1102,7 +1114,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B26" t="n">
@@ -1127,7 +1139,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B27" t="n">
@@ -1152,7 +1164,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B28" t="n">
@@ -1177,7 +1189,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B29" t="n">
@@ -1202,7 +1214,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B30" t="n">
@@ -1227,7 +1239,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B31" t="n">
@@ -1254,7 +1266,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B32" t="n">
@@ -1281,7 +1293,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B33" t="n">
@@ -1308,7 +1320,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B34" t="n">
@@ -1335,7 +1347,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B35" t="n">
@@ -1362,7 +1374,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B36" t="n">
@@ -1389,7 +1401,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B37" t="n">
@@ -1416,7 +1428,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B38" t="n">
@@ -1443,7 +1455,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B39" t="n">
@@ -1470,7 +1482,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B40" t="n">
@@ -1499,7 +1511,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B41" t="n">
@@ -1528,7 +1540,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B42" t="n">
@@ -1557,7 +1569,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B43" t="n">
@@ -1586,7 +1598,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B44" t="n">
@@ -1615,7 +1627,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B45" t="n">
@@ -1644,7 +1656,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B46" t="n">
@@ -1673,7 +1685,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B47" t="n">
@@ -1702,7 +1714,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B48" t="n">
@@ -1731,7 +1743,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B49" t="n">
@@ -1760,7 +1772,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B50" t="n">
@@ -1789,7 +1801,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B51" t="n">
@@ -1818,7 +1830,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B52" t="n">
@@ -1847,7 +1859,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B53" t="n">
@@ -1876,7 +1888,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B54" t="n">
@@ -1905,7 +1917,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B55" t="n">
@@ -1934,7 +1946,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B56" t="n">
@@ -1963,7 +1975,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B57" t="n">
@@ -1992,7 +2004,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B58" t="n">
@@ -2021,7 +2033,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B59" t="n">
@@ -2050,7 +2062,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B60" t="n">
@@ -2079,7 +2091,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B61" t="n">
@@ -2106,7 +2118,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B62" t="n">
@@ -2133,7 +2145,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B63" t="n">
@@ -2160,7 +2172,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B64" t="n">
@@ -2187,7 +2199,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B65" t="n">
@@ -2214,7 +2226,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B66" t="n">
@@ -2241,7 +2253,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B67" t="n">
@@ -2268,7 +2280,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B68" t="n">
@@ -2295,7 +2307,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B69" t="n">
@@ -2322,7 +2334,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B70" t="n">
@@ -2349,7 +2361,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B71" t="n">
@@ -2376,7 +2388,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B72" t="n">
@@ -2403,7 +2415,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B73" t="n">
@@ -2430,7 +2442,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B74" t="n">
@@ -2457,7 +2469,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B75" t="n">
@@ -2484,7 +2496,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B76" t="n">
@@ -2511,7 +2523,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B77" t="n">
@@ -2538,7 +2550,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B78" t="n">
@@ -2565,7 +2577,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B79" t="n">
@@ -2592,7 +2604,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B80" t="n">
@@ -2619,7 +2631,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B81" t="n">
@@ -2646,7 +2658,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B82" t="n">
@@ -2673,7 +2685,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B83" t="n">
@@ -2700,7 +2712,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B84" t="n">
@@ -2727,7 +2739,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B85" t="n">
@@ -2754,7 +2766,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B86" t="n">
@@ -2781,7 +2793,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B87" t="n">
@@ -2808,7 +2820,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B88" t="n">
@@ -2835,7 +2847,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B89" t="n">
@@ -2862,7 +2874,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B90" t="n">
@@ -2889,7 +2901,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B91" t="n">
@@ -2916,7 +2928,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B92" t="n">
@@ -2943,7 +2955,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B93" t="n">
@@ -2970,7 +2982,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B94" t="n">
@@ -2997,17 +3009,17 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B95" t="n">
-        <v>182.1100006103516</v>
+        <v>194.8200073242188</v>
       </c>
       <c r="C95" t="n">
-        <v>182.1100006103516</v>
+        <v>194.8200073242188</v>
       </c>
       <c r="D95" t="n">
-        <v>243264000</v>
+        <v>259837300</v>
       </c>
       <c r="E95" t="n">
         <v>-7.98</v>
@@ -3017,10 +3029,10 @@
         <v>399235889</v>
       </c>
       <c r="H95" t="n">
-        <v>72704847989.46425</v>
+        <v>77779138819.07098</v>
       </c>
       <c r="I95" t="n">
-        <v>0.6093239778851646</v>
+        <v>0.6508365283763354</v>
       </c>
     </row>
   </sheetData>
@@ -3052,75 +3064,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>43537</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -3156,13 +3168,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>43537</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -3198,13 +3210,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>43537</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -3240,13 +3252,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>43537</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -3273,7 +3285,7 @@
       <c r="I5" t="n">
         <v>-4.19</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>43537</v>
       </c>
       <c r="K5" t="n">
@@ -3286,13 +3298,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>43537</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -3319,7 +3331,7 @@
       <c r="I6" t="n">
         <v>-4.32</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>43537</v>
       </c>
       <c r="K6" t="n">
@@ -3332,13 +3344,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>43537</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -3365,7 +3377,7 @@
       <c r="I7" t="n">
         <v>-4.28</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>43537</v>
       </c>
       <c r="K7" t="n">
@@ -3378,13 +3390,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>43537</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -3411,7 +3423,7 @@
       <c r="I8" t="n">
         <v>-4.550000000000001</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>43537</v>
       </c>
       <c r="K8" t="n">
@@ -3424,13 +3436,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>43537</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -3457,7 +3469,7 @@
       <c r="I9" t="n">
         <v>-5.05</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>43537</v>
       </c>
       <c r="K9" t="n">
@@ -3470,13 +3482,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>43594</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -3503,7 +3515,7 @@
       <c r="I10" t="n">
         <v>-4.29</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>43594</v>
       </c>
       <c r="K10" t="n">
@@ -3516,13 +3528,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>43685</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -3549,7 +3561,7 @@
       <c r="I11" t="n">
         <v>-3.27</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>43685</v>
       </c>
       <c r="K11" t="n">
@@ -3562,13 +3574,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>43775</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -3595,7 +3607,7 @@
       <c r="I12" t="n">
         <v>-2.32</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>43775</v>
       </c>
       <c r="K12" t="n">
@@ -3608,13 +3620,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>43888</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -3641,7 +3653,7 @@
       <c r="I13" t="n">
         <v>-1.55</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>43888</v>
       </c>
       <c r="K13" t="n">
@@ -3654,13 +3666,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -3687,7 +3699,7 @@
       <c r="I14" t="n">
         <v>-1.5</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="K14" t="n">
@@ -3700,13 +3712,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>44413</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -3733,7 +3745,7 @@
       <c r="I15" t="n">
         <v>-1.4</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>44413</v>
       </c>
       <c r="K15" t="n">
@@ -3746,13 +3758,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>44504</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -3779,7 +3791,7 @@
       <c r="I16" t="n">
         <v>-1.62</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>44504</v>
       </c>
       <c r="K16" t="n">
@@ -3792,13 +3804,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>44617</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -3825,7 +3837,7 @@
       <c r="I17" t="n">
         <v>-1.96</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>44617</v>
       </c>
       <c r="K17" t="n">
@@ -3838,13 +3850,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -3871,7 +3883,7 @@
       <c r="I18" t="n">
         <v>1.23</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>44617</v>
       </c>
       <c r="K18" t="n">
@@ -3884,13 +3896,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>44413</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -3917,7 +3929,7 @@
       <c r="I19" t="n">
         <v>8</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>44617</v>
       </c>
       <c r="K19" t="n">
@@ -3930,13 +3942,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>44504</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -3963,7 +3975,7 @@
       <c r="I20" t="n">
         <v>16.29</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>44617</v>
       </c>
       <c r="K20" t="n">
@@ -3976,13 +3988,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>44617</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -4009,7 +4021,7 @@
       <c r="I21" t="n">
         <v>28.29</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>44617</v>
       </c>
       <c r="K21" t="n">
@@ -4022,13 +4034,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>44685</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -4055,7 +4067,7 @@
       <c r="I22" t="n">
         <v>34.03</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>44685</v>
       </c>
       <c r="K22" t="n">
@@ -4068,13 +4080,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>44776</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -4101,7 +4113,7 @@
       <c r="I23" t="n">
         <v>32.81</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>44776</v>
       </c>
       <c r="K23" t="n">
@@ -4114,13 +4126,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -4147,7 +4159,7 @@
       <c r="I24" t="n">
         <v>27.64</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="K24" t="n">
@@ -4160,13 +4172,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>44981</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -4193,7 +4205,7 @@
       <c r="I25" t="n">
         <v>20.12</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>44981</v>
       </c>
       <c r="K25" t="n">
@@ -4206,13 +4218,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -4239,7 +4251,7 @@
       <c r="I26" t="n">
         <v>11.73</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="K26" t="n">
@@ -4252,13 +4264,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -4285,7 +4297,7 @@
       <c r="I27" t="n">
         <v>2.869999999999999</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="K27" t="n">
@@ -4298,13 +4310,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>45233</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -4331,7 +4343,7 @@
       <c r="I28" t="n">
         <v>-9.19</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>45233</v>
       </c>
       <c r="K28" t="n">
@@ -4344,13 +4356,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>45345</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -4377,7 +4389,7 @@
       <c r="I29" t="n">
         <v>-12.33</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>45345</v>
       </c>
       <c r="K29" t="n">
@@ -4390,13 +4402,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -4423,7 +4435,7 @@
       <c r="I30" t="n">
         <v>-15.59</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="K30" t="n">
@@ -4436,13 +4448,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -4469,7 +4481,7 @@
       <c r="I31" t="n">
         <v>-15.3</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="K31" t="n">
@@ -4482,13 +4494,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>45603</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -4515,7 +4527,7 @@
       <c r="I32" t="n">
         <v>-5.740000000000001</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>45603</v>
       </c>
       <c r="K32" t="n">
@@ -4528,13 +4540,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -4561,7 +4573,7 @@
       <c r="I33" t="n">
         <v>-9.279999999999999</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="K33" t="n">
@@ -4574,13 +4586,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -4607,7 +4619,7 @@
       <c r="I34" t="n">
         <v>-8.729999999999999</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="K34" t="n">
@@ -4620,13 +4632,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -4653,7 +4665,7 @@
       <c r="I35" t="n">
         <v>-7.529999999999999</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="K35" t="n">
@@ -4666,13 +4678,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -4699,7 +4711,7 @@
       <c r="I36" t="n">
         <v>-8.069999999999999</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="K36" t="n">
@@ -4712,13 +4724,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>46073</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -4745,7 +4757,7 @@
       <c r="I37" t="n">
         <v>-7.26</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>46073</v>
       </c>
       <c r="K37" t="n">
@@ -4758,13 +4770,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -4791,7 +4803,7 @@
       <c r="I38" t="n">
         <v>-8.140000000000001</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="K38" t="n">
@@ -4804,13 +4816,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -4837,7 +4849,7 @@
       <c r="I39" t="n">
         <v>-7.98</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="K39" t="n">
@@ -4874,52 +4886,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>43530</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>43537</v>
       </c>
       <c r="C2" t="n">
@@ -4948,10 +4960,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>43584</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>43594</v>
       </c>
       <c r="C3" t="n">
@@ -4980,10 +4992,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>43677</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>43685</v>
       </c>
       <c r="C4" t="n">
@@ -5012,10 +5024,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>43769</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>43775</v>
       </c>
       <c r="C5" t="n">
@@ -5044,10 +5056,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>43887</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>43888</v>
       </c>
       <c r="C6" t="n">
@@ -5076,10 +5088,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>43951</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="C7" t="n">
@@ -5108,10 +5120,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>44043</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="C8" t="n">
@@ -5140,10 +5152,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>44124</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="C9" t="n">
@@ -5172,10 +5184,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>44243</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>44253</v>
       </c>
       <c r="C10" t="n">
@@ -5204,10 +5216,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>44316</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="C11" t="n">
@@ -5236,10 +5248,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>44407</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>44413</v>
       </c>
       <c r="C12" t="n">
@@ -5268,10 +5280,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>44498</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>44504</v>
       </c>
       <c r="C13" t="n">
@@ -5300,10 +5312,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>44610</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>44617</v>
       </c>
       <c r="C14" t="n">
@@ -5332,10 +5344,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>44680</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>44685</v>
       </c>
       <c r="C15" t="n">
@@ -5364,10 +5376,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>44771</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>44776</v>
       </c>
       <c r="C16" t="n">
@@ -5396,10 +5408,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>44865</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="C17" t="n">
@@ -5428,10 +5440,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>44974</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>44981</v>
       </c>
       <c r="C18" t="n">
@@ -5460,10 +5472,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>45044</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="C19" t="n">
@@ -5492,10 +5504,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>45138</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="C20" t="n">
@@ -5524,10 +5536,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>45226</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>45233</v>
       </c>
       <c r="C21" t="n">
@@ -5556,10 +5568,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>45338</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>45345</v>
       </c>
       <c r="C22" t="n">
@@ -5588,10 +5600,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>45408</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="C23" t="n">
@@ -5620,10 +5632,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>45499</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="C24" t="n">
@@ -5652,10 +5664,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>45596</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>45603</v>
       </c>
       <c r="C25" t="n">
@@ -5684,10 +5696,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>45702</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="C26" t="n">
@@ -5716,10 +5728,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>45772</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="C27" t="n">
@@ -5748,10 +5760,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>45863</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="C28" t="n">
@@ -5780,10 +5792,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>45961</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="C29" t="n">
@@ -5812,10 +5824,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>46066</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>46073</v>
       </c>
       <c r="C30" t="n">
@@ -5844,10 +5856,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>46136</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="C31" t="n">
@@ -5876,10 +5888,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>46227</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="C32" t="n">
@@ -5926,12 +5938,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
